--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -576,7 +576,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Locker 3</t>
@@ -666,7 +665,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -756,7 +754,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -846,7 +843,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Locker 11</t>
@@ -936,7 +932,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -1026,7 +1021,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -1116,7 +1110,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -1206,7 +1199,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -1296,7 +1288,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -1366,7 +1357,6 @@
           <t>IDP-782-4227-15-9321</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -1382,7 +1372,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -1452,7 +1441,6 @@
           <t>IP67</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -1468,7 +1456,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -1538,7 +1525,6 @@
           <t>ST6100-SXX</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -1554,7 +1540,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -1644,7 +1629,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -1734,7 +1718,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -1824,7 +1807,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -1894,7 +1876,6 @@
           <t>H985A</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -1910,7 +1891,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -2000,7 +1980,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -2090,7 +2069,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -2180,7 +2158,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -2270,7 +2247,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -2360,7 +2336,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -2450,7 +2425,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -2540,7 +2514,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -2630,7 +2603,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -2720,7 +2692,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -2810,7 +2781,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -2900,7 +2870,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -2970,7 +2939,6 @@
           <t>PMU 010000</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -2986,7 +2954,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -3076,7 +3043,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -3166,7 +3132,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -3256,7 +3221,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -3346,7 +3310,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -3436,7 +3399,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -3526,7 +3488,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -3616,7 +3577,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -3706,13 +3666,11 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -3792,7 +3750,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -3882,7 +3839,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -3947,8 +3903,6 @@
           <t>WTD /  ECI MULTIPLEXOR</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -3964,7 +3918,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4054,7 +4007,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4144,13 +4096,11 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -4230,7 +4180,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -4320,7 +4269,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4410,7 +4358,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -4500,7 +4447,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -4590,7 +4536,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4680,7 +4625,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4770,7 +4714,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4860,7 +4803,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -4950,7 +4892,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -5040,7 +4981,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -5130,7 +5070,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -5220,7 +5159,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -5310,7 +5248,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -5400,7 +5337,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -5490,7 +5426,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -5580,7 +5515,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -5670,7 +5604,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -5760,7 +5693,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -5850,7 +5782,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -5940,7 +5871,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -6030,7 +5960,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS</t>
@@ -6120,7 +6049,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -6210,7 +6138,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -6300,7 +6227,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -6390,7 +6316,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -6480,7 +6405,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -6570,7 +6494,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -6660,7 +6583,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -6750,7 +6672,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -6840,7 +6761,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -6930,7 +6850,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7020,7 +6939,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7110,7 +7028,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7200,7 +7117,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7290,7 +7206,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7380,7 +7295,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7470,7 +7384,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7560,7 +7473,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7650,7 +7562,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7740,7 +7651,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7830,7 +7740,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -7920,7 +7829,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8010,7 +7918,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8100,7 +8007,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8190,7 +8096,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8280,7 +8185,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -8370,7 +8274,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -8460,7 +8363,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -8550,7 +8452,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -8640,13 +8541,11 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -8726,7 +8625,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8816,7 +8714,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -8906,7 +8803,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -8996,7 +8892,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -9086,7 +8981,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -9176,7 +9070,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -9266,7 +9159,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9356,7 +9248,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9446,7 +9337,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -9536,7 +9426,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9626,7 +9515,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9716,7 +9604,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9806,7 +9693,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9896,7 +9782,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -9986,7 +9871,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10076,7 +9960,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10166,7 +10049,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10256,7 +10138,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10346,7 +10227,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10436,7 +10316,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10526,7 +10405,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10616,7 +10494,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10706,7 +10583,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10796,7 +10672,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10886,7 +10761,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -10976,7 +10850,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -11066,7 +10939,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -11156,7 +11028,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -11246,7 +11117,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -11336,7 +11206,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -11426,7 +11295,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -11516,7 +11384,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -11606,7 +11473,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -11696,7 +11562,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -11786,7 +11651,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -11876,7 +11740,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -11966,7 +11829,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -12056,7 +11918,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -12146,7 +12007,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -12236,7 +12096,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -12326,7 +12185,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -12416,7 +12274,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -12506,7 +12363,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -12596,7 +12452,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -12686,7 +12541,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -12776,7 +12630,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -12866,7 +12719,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -12903,7 +12755,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>2026-09-22T18:53:25</t>
+          <t>2026-09-24T17:28:26</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12808,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13046,7 +12897,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13136,7 +12986,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13226,7 +13075,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13316,7 +13164,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13406,7 +13253,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13496,7 +13342,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -13586,7 +13431,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -13676,7 +13520,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -13766,7 +13609,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -13857,7 +13699,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -13948,7 +13789,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -14038,7 +13878,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -14128,7 +13967,6 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>Locker 3</t>
@@ -14218,7 +14056,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14308,7 +14145,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14398,7 +14234,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14488,7 +14323,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -14578,7 +14412,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14668,7 +14501,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14758,7 +14590,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14848,7 +14679,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -14938,7 +14768,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -15008,7 +14837,6 @@
           <t>IDP-782-4227-15-9321</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -15024,7 +14852,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -15094,7 +14921,6 @@
           <t>IP67</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -15110,7 +14936,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -15180,7 +15005,6 @@
           <t>ST6100-SXX</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -15196,7 +15020,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -15286,7 +15109,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -15376,7 +15198,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -15466,7 +15287,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -15536,7 +15356,6 @@
           <t>H985A</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -15552,7 +15371,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -15642,7 +15460,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -15732,7 +15549,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -15822,7 +15638,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -15912,7 +15727,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -16002,7 +15816,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16092,7 +15905,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16182,7 +15994,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -16272,7 +16083,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16362,7 +16172,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16452,7 +16261,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16542,7 +16350,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -16612,7 +16419,6 @@
           <t>PMU 010000</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -16628,7 +16434,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16718,7 +16523,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -16808,7 +16612,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -16898,7 +16701,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -16988,7 +16790,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -17078,7 +16879,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -17168,7 +16968,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -17258,7 +17057,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -17348,13 +17146,11 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -17434,7 +17230,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -17524,7 +17319,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -17614,7 +17408,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -17704,7 +17497,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -17794,13 +17586,11 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -17880,7 +17670,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -17970,7 +17759,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -18060,7 +17848,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -18150,7 +17937,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -18240,7 +18026,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -18330,7 +18115,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -18420,7 +18204,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -18510,7 +18293,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -18600,7 +18382,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -18690,7 +18471,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -18780,7 +18560,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -18870,7 +18649,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -18960,7 +18738,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19050,7 +18827,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19140,7 +18916,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19230,7 +19005,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19320,7 +19094,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19410,7 +19183,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19500,7 +19272,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -19590,7 +19361,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -19680,7 +19450,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS</t>
@@ -19770,7 +19539,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19860,7 +19628,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -19950,7 +19717,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20040,7 +19806,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -20130,7 +19895,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -20220,7 +19984,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -20310,7 +20073,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20400,7 +20162,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20490,7 +20251,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20580,7 +20340,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20670,7 +20429,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -20760,7 +20518,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -20850,7 +20607,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -20940,7 +20696,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -21030,7 +20785,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21120,7 +20874,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21210,7 +20963,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21300,7 +21052,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21390,7 +21141,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21480,7 +21230,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21570,7 +21319,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21635,8 +21383,6 @@
           <t>WTD /  ECI MULTIPLEXOR</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -21652,7 +21398,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21742,7 +21487,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21832,7 +21576,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -21922,7 +21665,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -22012,7 +21754,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -22102,7 +21843,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -22192,7 +21932,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -22282,13 +22021,11 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -22368,7 +22105,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -22458,7 +22194,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -22548,7 +22283,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -22638,7 +22372,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -22728,7 +22461,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>Locker 3</t>
@@ -22818,7 +22550,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -22908,7 +22639,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -22998,7 +22728,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23088,7 +22817,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -23178,7 +22906,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23268,7 +22995,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23358,7 +23084,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23448,7 +23173,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23538,7 +23262,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -23628,7 +23351,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -23718,7 +23440,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -23808,7 +23529,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>Locker 11</t>
@@ -23898,7 +23618,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -23988,7 +23707,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24078,7 +23796,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24168,7 +23885,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24258,7 +23974,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24348,7 +24063,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24438,7 +24152,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24528,7 +24241,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24618,7 +24330,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -24708,7 +24419,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -24799,7 +24509,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -24890,7 +24599,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -24980,7 +24688,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -25070,7 +24777,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -25160,7 +24866,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -25250,7 +24955,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -25340,7 +25044,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -25430,7 +25133,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -25520,7 +25222,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -25610,7 +25311,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -25700,7 +25400,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -25790,7 +25489,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -25880,7 +25578,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -25970,7 +25667,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -26060,7 +25756,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -26150,7 +25845,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -26240,7 +25934,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -26330,7 +26023,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -26420,7 +26112,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -26510,7 +26201,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -26600,7 +26290,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -26690,7 +26379,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -26780,7 +26468,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -26870,7 +26557,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -26960,7 +26646,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -27050,7 +26735,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -27140,7 +26824,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -27230,7 +26913,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -27320,7 +27002,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -27410,7 +27091,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -27500,7 +27180,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -27590,7 +27269,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -27680,7 +27358,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -27770,7 +27447,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -27860,7 +27536,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -27950,7 +27625,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28040,7 +27714,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -28130,7 +27803,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28220,7 +27892,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28310,7 +27981,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28400,7 +28070,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28490,7 +28159,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28560,7 +28228,6 @@
           <t>IDP-782-4227-15-9321</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -28576,7 +28243,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -28646,7 +28312,6 @@
           <t>IP67</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -28662,7 +28327,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -28732,7 +28396,6 @@
           <t>ST6100-SXX</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -28748,7 +28411,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -28838,7 +28500,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -28928,7 +28589,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -29018,7 +28678,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -29088,7 +28747,6 @@
           <t>H985A</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -29104,7 +28762,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -29194,7 +28851,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -29284,7 +28940,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -29374,7 +29029,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -29464,7 +29118,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -29554,7 +29207,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -29644,7 +29296,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -29734,7 +29385,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -29824,7 +29474,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -29914,7 +29563,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -30004,7 +29652,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -30094,7 +29741,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -30164,7 +29810,6 @@
           <t>PMU 010000</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -30180,7 +29825,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -30270,7 +29914,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -30360,7 +30003,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -30450,7 +30092,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -30540,7 +30181,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -30630,7 +30270,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -30720,7 +30359,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -30810,7 +30448,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -30900,13 +30537,11 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -30986,7 +30621,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -31076,7 +30710,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -31166,7 +30799,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -31256,7 +30888,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -31346,13 +30977,11 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -31432,7 +31061,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -31522,7 +31150,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -31612,7 +31239,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -31702,7 +31328,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -31792,7 +31417,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -31882,7 +31506,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -31972,7 +31595,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32062,7 +31684,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32152,7 +31773,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -32242,7 +31862,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -32332,7 +31951,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32422,7 +32040,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32512,7 +32129,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32602,7 +32218,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32692,7 +32307,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32782,7 +32396,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32872,7 +32485,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -32962,7 +32574,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -33052,7 +32663,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -33142,7 +32752,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -33232,7 +32841,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS</t>
@@ -33322,7 +32930,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -33412,7 +33019,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -33502,7 +33108,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -33592,7 +33197,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -33682,7 +33286,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -33772,7 +33375,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -33862,7 +33464,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -33952,7 +33553,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -34042,7 +33642,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -34132,7 +33731,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -34222,7 +33820,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34312,7 +33909,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34402,7 +33998,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -34492,7 +34087,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -34582,7 +34176,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34672,7 +34265,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34762,7 +34354,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34852,7 +34443,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -34942,7 +34532,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35032,7 +34621,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35122,7 +34710,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35187,8 +34774,6 @@
           <t>WTD /  ECI MULTIPLEXOR</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -35204,7 +34789,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35294,7 +34878,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35384,7 +34967,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -35474,7 +35056,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -35564,7 +35145,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -35654,7 +35234,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -35744,7 +35323,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -35834,13 +35412,11 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -35920,7 +35496,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -36010,7 +35585,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -36100,7 +35674,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -36190,7 +35763,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -36280,7 +35852,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
           <t>Locker 3</t>
@@ -36370,7 +35941,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -36460,7 +36030,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -36550,7 +36119,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -36640,7 +36208,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -36730,7 +36297,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -36820,7 +36386,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -36910,7 +36475,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -37000,7 +36564,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -37090,7 +36653,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -37180,7 +36742,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37270,7 +36831,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37360,7 +36920,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr">
         <is>
           <t>Locker 11</t>
@@ -37450,7 +37009,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37540,7 +37098,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37630,7 +37187,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37720,7 +37276,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37810,7 +37365,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37900,7 +37454,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -37990,7 +37543,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -38080,7 +37632,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -38170,7 +37721,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -38260,7 +37810,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -38351,7 +37900,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -38442,7 +37990,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -38532,7 +38079,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -38622,7 +38168,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -38712,7 +38257,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -38802,7 +38346,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -38892,7 +38435,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -38982,7 +38524,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -39072,7 +38613,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -39162,7 +38702,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39252,7 +38791,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39342,7 +38880,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39432,7 +38969,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39522,7 +39058,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39612,7 +39147,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39702,7 +39236,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39792,7 +39325,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -39882,7 +39414,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -39972,7 +39503,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -40062,7 +39592,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -40152,7 +39681,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -40242,7 +39770,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -40332,7 +39859,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -40422,7 +39948,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -40512,7 +40037,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -40602,7 +40126,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -40692,7 +40215,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -40782,7 +40304,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -40872,7 +40393,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -40962,7 +40482,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -41052,7 +40571,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -41142,7 +40660,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41232,7 +40749,6 @@
           <t>PRESTAMO</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -41322,7 +40838,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41412,7 +40927,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41502,7 +41016,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41592,7 +41105,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -41682,7 +41194,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41772,7 +41283,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41862,7 +41372,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -41952,7 +41461,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -42042,7 +41550,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -42112,7 +41619,6 @@
           <t>IDP-782-4227-15-9321</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -42128,7 +41634,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -42198,7 +41703,6 @@
           <t>IP67</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -42214,7 +41718,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -42284,7 +41787,6 @@
           <t>ST6100-SXX</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -42300,7 +41802,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -42390,7 +41891,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -42480,7 +41980,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -42570,7 +42069,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -42640,7 +42138,6 @@
           <t>H985A</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -42656,7 +42153,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -42746,7 +42242,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -42836,7 +42331,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -42926,7 +42420,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -43016,7 +42509,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -43106,7 +42598,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43196,7 +42687,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43286,7 +42776,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -43376,7 +42865,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43466,7 +42954,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43556,7 +43043,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43646,7 +43132,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -43716,7 +43201,6 @@
           <t>PMU 010000</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -43732,7 +43216,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43822,7 +43305,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -43912,7 +43394,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -44002,7 +43483,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -44092,7 +43572,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -44182,7 +43661,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -44272,7 +43750,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -44362,7 +43839,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -44452,13 +43928,11 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M491" t="inlineStr"/>
       <c r="N491" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -44538,7 +44012,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -44628,7 +44101,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -44718,7 +44190,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -44808,7 +44279,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -44898,13 +44368,11 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr">
         <is>
           <t>ESTANTE PRIMER PISO</t>
         </is>
       </c>
-      <c r="M496" t="inlineStr"/>
       <c r="N496" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -44984,7 +44452,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -45074,7 +44541,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -45164,7 +44630,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -45254,7 +44719,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -45344,7 +44808,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -45434,7 +44897,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -45524,7 +44986,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -45614,7 +45075,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -45704,7 +45164,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -45794,7 +45253,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
           <t>Locker 17</t>
@@ -45884,7 +45342,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -45974,7 +45431,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46064,7 +45520,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46154,7 +45609,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46244,7 +45698,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46334,7 +45787,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46424,7 +45876,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46514,7 +45965,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46604,7 +46054,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -46694,7 +46143,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -46784,7 +46232,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS</t>
@@ -46874,7 +46321,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -46964,7 +46410,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47054,7 +46499,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47144,7 +46588,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -47234,7 +46677,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -47324,7 +46766,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -47414,7 +46855,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47504,7 +46944,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47594,7 +47033,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47684,7 +47122,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -47774,7 +47211,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -47864,7 +47300,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -47954,7 +47389,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -48044,7 +47478,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
       <c r="L531" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -48134,7 +47567,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48224,7 +47656,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48314,7 +47745,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48404,7 +47834,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
       <c r="L535" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48494,7 +47923,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48584,7 +48012,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
       <c r="L537" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48674,7 +48101,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48739,8 +48165,6 @@
           <t>WTD /  ECI MULTIPLEXOR</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
           <t>Unidades</t>
@@ -48756,7 +48180,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48846,7 +48269,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -48936,7 +48358,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
       <c r="L541" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -49026,7 +48447,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -49116,7 +48536,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
       <c r="L543" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -49206,7 +48625,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -49296,7 +48714,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
       <c r="L545" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -49386,13 +48803,11 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
       <c r="L546" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
         </is>
       </c>
-      <c r="M546" t="inlineStr"/>
       <c r="N546" t="inlineStr">
         <is>
           <t>ACTIVO</t>
@@ -49472,7 +48887,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
       <c r="L547" t="inlineStr">
         <is>
           <t>Locker 19</t>
@@ -49562,7 +48976,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr">
         <is>
           <t>Locker 20</t>
@@ -49652,7 +49065,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -49742,7 +49154,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -49832,7 +49243,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr">
         <is>
           <t>Locker 3</t>
@@ -49922,7 +49332,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -50012,7 +49421,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50102,7 +49510,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50192,7 +49599,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -50282,7 +49688,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
       <c r="L556" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50372,7 +49777,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
       <c r="L557" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50462,7 +49866,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
       <c r="L558" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50552,7 +49955,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50642,7 +50044,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
       <c r="L560" t="inlineStr">
         <is>
           <t>Locker 12</t>
@@ -50732,7 +50133,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
       <c r="L561" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -50822,7 +50222,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -50912,7 +50311,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr">
         <is>
           <t>Locker 11</t>
@@ -51002,7 +50400,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
       <c r="L564" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51092,7 +50489,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51182,7 +50578,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51272,7 +50667,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
       <c r="L567" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51362,7 +50756,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
       <c r="L568" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51452,7 +50845,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51542,7 +50934,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51632,7 +51023,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51722,7 +51112,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
       <c r="L572" t="inlineStr">
         <is>
           <t>10-11</t>
@@ -51812,7 +51201,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -51903,7 +51291,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -51994,7 +51381,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr">
         <is>
           <t>12-13</t>
@@ -52084,7 +51470,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr">
         <is>
           <t>MODULO DE MEDIDORES SATEC</t>
@@ -52174,7 +51559,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -52264,7 +51648,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -52354,7 +51737,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -52444,7 +51826,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -52534,7 +51915,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
       <c r="L581" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -52624,7 +52004,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
       <c r="L582" t="inlineStr">
         <is>
           <t>Locker 23</t>
@@ -52714,7 +52093,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
       <c r="L583" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -52804,7 +52182,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
       <c r="L584" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -52894,7 +52271,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -52984,7 +52360,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
       <c r="L586" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53074,7 +52449,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53164,7 +52538,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53254,7 +52627,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
       <c r="L589" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53344,7 +52716,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
       <c r="L590" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53434,7 +52805,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -53524,7 +52894,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
       <c r="L592" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -53614,7 +52983,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -53704,7 +53072,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
       <c r="L594" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -53794,7 +53161,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -53884,7 +53250,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr">
         <is>
           <t>Locker 22</t>
@@ -53974,7 +53339,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr">
         <is>
           <t>Locker 16</t>
@@ -54064,7 +53428,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -54154,7 +53517,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -54244,7 +53606,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -54334,7 +53695,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
         <is>
           <t>Locker 15</t>
@@ -54424,7 +53784,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
           <t>MODULO DE SWITCHES</t>
@@ -54514,7 +53873,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
           <t>MODULO DE EQUIPOS VALIANT</t>
@@ -54604,7 +53962,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
           <t>Locker 21</t>
@@ -54694,7 +54051,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
           <t>Locker 24</t>
@@ -54784,7 +54140,6 @@
           <t>EQUIPO CIBERSEGURIDAD</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
           <t>Locker 23</t>
